--- a/gamer_forms/009_rpg_character_background_form--gamer_forms.xlsx
+++ b/gamer_forms/009_rpg_character_background_form--gamer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'one-shot'}</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'One-Shot'}</t>
+          <t>One-Shot</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'campaign'}</t>
+          <t>campaign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Campaign'}</t>
+          <t>Campaign</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'community_event'}</t>
+          <t>community_event</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Community Event'}</t>
+          <t>Community Event</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fighter'}</t>
+          <t>fighter</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Fighter'}</t>
+          <t>Fighter</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rogue'}</t>
+          <t>rogue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rogue'}</t>
+          <t>Rogue</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wizard'}</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wizard'}</t>
+          <t>Wizard</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'human'}</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Human'}</t>
+          <t>Human</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'elf'}</t>
+          <t>elf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Elf'}</t>
+          <t>Elf</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'dwarf'}</t>
+          <t>dwarf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Dwarf'}</t>
+          <t>Dwarf</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chaotic'}</t>
+          <t>chaotic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Chaotic'}</t>
+          <t>Chaotic</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lawful'}</t>
+          <t>lawful</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lawful'}</t>
+          <t>Lawful</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'balanced'}</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Balanced'}</t>
+          <t>Balanced</t>
         </is>
       </c>
     </row>
